--- a/.schema/MHR_SHOKUI_NINKA.xlsx
+++ b/.schema/MHR_SHOKUI_NINKA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_fuk\git\sample\.schema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B41E075-58BB-44B1-9B6E-B2360A1EC2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MHR_SHOKUI_NINKA" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMARF.MHR_SHOKUI_NINKA!$A$2:$J$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">EMARF.MHR_SHOKUI_NINKA!$2:$2</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -586,14 +586,14 @@
       <c r="F3" s="6"/>
       <c r="G3" s="7">
         <f t="shared" ref="G3:G12" ca="1" si="0">NOW()</f>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="H3" s="4">
         <v>0</v>
       </c>
       <c r="I3" s="7">
         <f t="shared" ref="I3:I12" ca="1" si="1">NOW()</f>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="J3" s="4">
         <v>0</v>
@@ -626,14 +626,14 @@
       <c r="F4" s="6"/>
       <c r="G4" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="H4" s="4">
         <v>0</v>
       </c>
       <c r="I4" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="J4" s="4">
         <v>0</v>
@@ -685,14 +685,14 @@
       <c r="F5" s="6"/>
       <c r="G5" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="H5" s="4">
         <v>0</v>
       </c>
       <c r="I5" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="J5" s="4">
         <v>0</v>
@@ -747,14 +747,14 @@
       <c r="F6" s="6"/>
       <c r="G6" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="H6" s="4">
         <v>0</v>
       </c>
       <c r="I6" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="J6" s="4">
         <v>0</v>
@@ -809,14 +809,14 @@
       <c r="F7" s="6"/>
       <c r="G7" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="H7" s="4">
         <v>0</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="J7" s="4">
         <v>0</v>
@@ -871,14 +871,14 @@
       <c r="F8" s="6"/>
       <c r="G8" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="H8" s="4">
         <v>0</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="J8" s="4">
         <v>0</v>
@@ -933,14 +933,14 @@
       <c r="F9" s="6"/>
       <c r="G9" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="J9" s="4">
         <v>0</v>
@@ -995,14 +995,14 @@
       <c r="F10" s="6"/>
       <c r="G10" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="H10" s="4">
         <v>0</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="J10" s="4">
         <v>0</v>
@@ -1057,14 +1057,14 @@
       <c r="F11" s="6"/>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="H11" s="4">
         <v>0</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="J11" s="4">
         <v>0</v>
@@ -1119,14 +1119,14 @@
       <c r="F12" s="6"/>
       <c r="G12" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="H12" s="4">
         <v>0</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.454815740741</v>
+        <v>46282.559396643519</v>
       </c>
       <c r="J12" s="4">
         <v>0</v>

--- a/.schema/MHR_SHOKUI_NINKA.xlsx
+++ b/.schema/MHR_SHOKUI_NINKA.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B41E075-58BB-44B1-9B6E-B2360A1EC2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61099E91-B169-4484-ACFE-6BF3E16FF0BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43200" yWindow="7800" windowWidth="14400" windowHeight="7800" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MHR_SHOKUI_NINKA" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMARF.MHR_SHOKUI_NINKA!$A$2:$J$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">EMARF.MHR_SHOKUI_NINKA!$2:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMARF.MHR_SHOKUI_NINKA!$A$1:$J$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">EMARF.MHR_SHOKUI_NINKA!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="19">
   <si>
     <t>BUSHO_ID</t>
   </si>
@@ -136,7 +136,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,6 +162,12 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -211,7 +217,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -234,6 +240,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -498,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U74"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="6" width="6.5" style="1" bestFit="1" customWidth="1"/>
@@ -509,131 +521,190 @@
     <col min="11" max="11" width="8.796875" style="1"/>
     <col min="12" max="19" width="4.09765625" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="4.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.796875" style="1"/>
+    <col min="21" max="21" width="5.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="13.2" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="1:21" s="3" customFormat="1" ht="86.4" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="86.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L1" s="3">
         <v>128</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M1" s="3">
         <v>64</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N1" s="3">
         <v>32</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O1" s="3">
         <v>16</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P1" s="3">
         <v>8</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q1" s="3">
         <v>4</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R1" s="3">
         <v>2</v>
       </c>
-      <c r="S2" s="3">
-        <v>1</v>
-      </c>
+      <c r="S1" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="13.2" x14ac:dyDescent="0.45">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="4">
+        <v>255</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="7">
+        <f t="shared" ref="G2:G65" ca="1" si="0">NOW()</f>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="7">
+        <f t="shared" ref="I2:I65" ca="1" si="1">NOW()</f>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
     </row>
     <row r="3" spans="1:21" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A3" s="4">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4">
-        <v>26</v>
+        <v>1</v>
+      </c>
+      <c r="B3" s="8">
+        <v>2</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="4">
-        <v>255</v>
+        <f t="shared" ref="D3:D11" si="2">T3</f>
+        <v>0</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="7">
-        <f t="shared" ref="G3:G12" ca="1" si="0">NOW()</f>
-        <v>46282.559396643519</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
       </c>
       <c r="H3" s="4">
         <v>0</v>
       </c>
       <c r="I3" s="7">
-        <f t="shared" ref="I3:I12" ca="1" si="1">NOW()</f>
-        <v>46282.559396643519</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
       </c>
       <c r="J3" s="4">
         <v>0</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0</v>
+      </c>
+      <c r="T3" s="1">
+        <f t="shared" ref="T3:T11" si="3">SUMPRODUCT(L$1:S$1,L3:S3)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:21" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A4" s="4">
-        <v>6</v>
-      </c>
-      <c r="B4" s="4">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="B4" s="8">
+        <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:D12" si="2">T4</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="H4" s="4">
         <v>0</v>
       </c>
       <c r="I4" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="J4" s="4">
         <v>0</v>
@@ -660,39 +731,42 @@
         <v>0</v>
       </c>
       <c r="S4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" s="1">
-        <f t="shared" ref="T4:T12" si="3">SUMPRODUCT(L$2:S$2,L4:S4)</f>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A5" s="4">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4">
-        <v>28</v>
+        <v>1</v>
+      </c>
+      <c r="B5" s="8">
+        <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="H5" s="4">
         <v>0</v>
       </c>
       <c r="I5" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="J5" s="4">
         <v>0</v>
@@ -716,45 +790,45 @@
         <v>0</v>
       </c>
       <c r="R5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="1">
         <v>1</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A6" s="4">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4">
-        <v>29</v>
+        <v>1</v>
+      </c>
+      <c r="B6" s="8">
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="H6" s="4">
         <v>0</v>
       </c>
       <c r="I6" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="J6" s="4">
         <v>0</v>
@@ -775,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="1">
         <v>1</v>
@@ -785,38 +859,38 @@
       </c>
       <c r="T6" s="1">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A7" s="4">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8">
         <v>6</v>
-      </c>
-      <c r="B7" s="4">
-        <v>30</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="H7" s="4">
         <v>0</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="J7" s="4">
         <v>0</v>
@@ -834,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="1">
         <v>1</v>
@@ -847,38 +921,38 @@
       </c>
       <c r="T7" s="1">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A8" s="4">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4">
-        <v>31</v>
+        <v>1</v>
+      </c>
+      <c r="B8" s="8">
+        <v>7</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="H8" s="4">
         <v>0</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="J8" s="4">
         <v>0</v>
@@ -893,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="1">
         <v>1</v>
@@ -909,38 +983,38 @@
       </c>
       <c r="T8" s="1">
         <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="U8" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A9" s="4">
-        <v>6</v>
-      </c>
-      <c r="B9" s="4">
-        <v>32</v>
+        <v>1</v>
+      </c>
+      <c r="B9" s="8">
+        <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="2"/>
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="J9" s="4">
         <v>0</v>
@@ -952,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="1">
         <v>1</v>
@@ -971,38 +1045,38 @@
       </c>
       <c r="T9" s="1">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A10" s="4">
-        <v>6</v>
-      </c>
-      <c r="B10" s="4">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="B10" s="8">
+        <v>9</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="H10" s="4">
         <v>0</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="J10" s="4">
         <v>0</v>
@@ -1011,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="1">
         <v>1</v>
@@ -1033,44 +1107,44 @@
       </c>
       <c r="T10" s="1">
         <f t="shared" si="3"/>
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="13.2" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="4">
-        <v>6</v>
-      </c>
-      <c r="B11" s="4">
-        <v>34</v>
+        <v>1</v>
+      </c>
+      <c r="B11" s="8">
+        <v>10</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="2"/>
-        <v>127</v>
+        <v>255</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="H11" s="4">
         <v>0</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="J11" s="4">
         <v>0</v>
       </c>
       <c r="L11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="1">
         <v>1</v>
@@ -1095,76 +1169,1904 @@
       </c>
       <c r="T11" s="1">
         <f t="shared" si="3"/>
-        <v>127</v>
+        <v>255</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="4">
-        <v>6</v>
-      </c>
-      <c r="B12" s="4">
-        <v>35</v>
+      <c r="A12" s="9">
+        <v>1</v>
+      </c>
+      <c r="B12" s="5">
+        <v>14</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="4">
-        <f t="shared" si="2"/>
         <v>255</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="H12" s="4">
         <v>0</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559396643519</v>
+        <v>46316.442834374997</v>
       </c>
       <c r="J12" s="4">
         <v>0</v>
       </c>
-      <c r="L12" s="1">
-        <v>1</v>
-      </c>
-      <c r="M12" s="1">
-        <v>1</v>
-      </c>
-      <c r="N12" s="1">
-        <v>1</v>
-      </c>
-      <c r="O12" s="1">
-        <v>1</v>
-      </c>
-      <c r="P12" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>1</v>
-      </c>
-      <c r="R12" s="1">
-        <v>1</v>
-      </c>
-      <c r="S12" s="1">
-        <v>1</v>
-      </c>
-      <c r="T12" s="1">
-        <f t="shared" si="3"/>
-        <v>255</v>
-      </c>
-      <c r="U12" s="1" t="s">
+    </row>
+    <row r="13" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="9">
+        <v>2</v>
+      </c>
+      <c r="B13" s="5">
+        <v>20</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4">
+        <v>255</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="9">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5">
+        <v>22</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="4">
+        <v>255</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="9">
+        <v>4</v>
+      </c>
+      <c r="B15" s="5">
+        <v>22</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="4">
+        <v>255</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="9">
+        <v>5</v>
+      </c>
+      <c r="B16" s="5">
+        <v>22</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="4">
+        <v>255</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
+      </c>
+      <c r="I16" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="9">
+        <v>6</v>
+      </c>
+      <c r="B17" s="5">
+        <v>23</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="4">
+        <v>255</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="9">
+        <v>7</v>
+      </c>
+      <c r="B18" s="5">
+        <v>23</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="4">
+        <v>255</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="9">
+        <v>8</v>
+      </c>
+      <c r="B19" s="5">
+        <v>23</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="4">
+        <v>255</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="9">
+        <v>9</v>
+      </c>
+      <c r="B20" s="5">
+        <v>23</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="4">
+        <v>255</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0</v>
+      </c>
+      <c r="I20" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="9">
+        <v>10</v>
+      </c>
+      <c r="B21" s="5">
+        <v>23</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="4">
+        <v>255</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0</v>
+      </c>
+      <c r="I21" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="9">
+        <v>11</v>
+      </c>
+      <c r="B22" s="5">
+        <v>23</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="4">
+        <v>255</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0</v>
+      </c>
+      <c r="I22" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="9">
+        <v>12</v>
+      </c>
+      <c r="B23" s="5">
+        <v>23</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="4">
+        <v>255</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H23" s="4">
+        <v>0</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="9">
+        <v>13</v>
+      </c>
+      <c r="B24" s="5">
+        <v>25</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="4">
+        <v>255</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H24" s="4">
+        <v>0</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="9">
+        <v>14</v>
+      </c>
+      <c r="B25" s="5">
+        <v>25</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="4">
+        <v>255</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H25" s="4">
+        <v>0</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="9">
+        <v>15</v>
+      </c>
+      <c r="B26" s="5">
+        <v>25</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="4">
+        <v>255</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H26" s="4">
+        <v>0</v>
+      </c>
+      <c r="I26" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J26" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="9">
+        <v>16</v>
+      </c>
+      <c r="B27" s="5">
+        <v>25</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="4">
+        <v>255</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H27" s="4">
+        <v>0</v>
+      </c>
+      <c r="I27" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="9">
+        <v>17</v>
+      </c>
+      <c r="B28" s="5">
+        <v>25</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="4">
+        <v>255</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H28" s="4">
+        <v>0</v>
+      </c>
+      <c r="I28" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J28" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="9">
         <v>18</v>
       </c>
+      <c r="B29" s="5">
+        <v>25</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="4">
+        <v>255</v>
+      </c>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H29" s="4">
+        <v>0</v>
+      </c>
+      <c r="I29" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="9">
+        <v>19</v>
+      </c>
+      <c r="B30" s="5">
+        <v>25</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="4">
+        <v>255</v>
+      </c>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H30" s="4">
+        <v>0</v>
+      </c>
+      <c r="I30" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="9">
+        <v>20</v>
+      </c>
+      <c r="B31" s="5">
+        <v>25</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="4">
+        <v>255</v>
+      </c>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H31" s="4">
+        <v>0</v>
+      </c>
+      <c r="I31" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="9">
+        <v>21</v>
+      </c>
+      <c r="B32" s="5">
+        <v>25</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="4">
+        <v>255</v>
+      </c>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H32" s="4">
+        <v>0</v>
+      </c>
+      <c r="I32" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="9">
+        <v>22</v>
+      </c>
+      <c r="B33" s="5">
+        <v>25</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="4">
+        <v>255</v>
+      </c>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H33" s="4">
+        <v>0</v>
+      </c>
+      <c r="I33" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J33" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="9">
+        <v>23</v>
+      </c>
+      <c r="B34" s="5">
+        <v>25</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="4">
+        <v>255</v>
+      </c>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H34" s="4">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J34" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="9">
+        <v>24</v>
+      </c>
+      <c r="B35" s="5">
+        <v>25</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="4">
+        <v>255</v>
+      </c>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H35" s="4">
+        <v>0</v>
+      </c>
+      <c r="I35" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="9">
+        <v>25</v>
+      </c>
+      <c r="B36" s="5">
+        <v>25</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="4">
+        <v>255</v>
+      </c>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H36" s="4">
+        <v>0</v>
+      </c>
+      <c r="I36" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J36" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="9">
+        <v>26</v>
+      </c>
+      <c r="B37" s="5">
+        <v>25</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="4">
+        <v>255</v>
+      </c>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H37" s="4">
+        <v>0</v>
+      </c>
+      <c r="I37" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J37" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="9">
+        <v>27</v>
+      </c>
+      <c r="B38" s="5">
+        <v>25</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="4">
+        <v>255</v>
+      </c>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H38" s="4">
+        <v>0</v>
+      </c>
+      <c r="I38" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J38" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="9">
+        <v>28</v>
+      </c>
+      <c r="B39" s="5">
+        <v>25</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="4">
+        <v>255</v>
+      </c>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H39" s="4">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J39" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="9">
+        <v>29</v>
+      </c>
+      <c r="B40" s="5">
+        <v>25</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="4">
+        <v>255</v>
+      </c>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H40" s="4">
+        <v>0</v>
+      </c>
+      <c r="I40" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J40" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="9">
+        <v>30</v>
+      </c>
+      <c r="B41" s="5">
+        <v>26</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="4">
+        <v>255</v>
+      </c>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H41" s="4">
+        <v>0</v>
+      </c>
+      <c r="I41" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J41" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="9">
+        <v>31</v>
+      </c>
+      <c r="B42" s="5">
+        <v>26</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="4">
+        <v>255</v>
+      </c>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H42" s="4">
+        <v>0</v>
+      </c>
+      <c r="I42" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J42" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="9">
+        <v>32</v>
+      </c>
+      <c r="B43" s="5">
+        <v>26</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="4">
+        <v>255</v>
+      </c>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H43" s="4">
+        <v>0</v>
+      </c>
+      <c r="I43" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J43" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="9">
+        <v>33</v>
+      </c>
+      <c r="B44" s="5">
+        <v>26</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="4">
+        <v>255</v>
+      </c>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H44" s="4">
+        <v>0</v>
+      </c>
+      <c r="I44" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J44" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="9">
+        <v>34</v>
+      </c>
+      <c r="B45" s="5">
+        <v>26</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="4">
+        <v>255</v>
+      </c>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H45" s="4">
+        <v>0</v>
+      </c>
+      <c r="I45" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J45" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="9">
+        <v>35</v>
+      </c>
+      <c r="B46" s="5">
+        <v>26</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="4">
+        <v>255</v>
+      </c>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H46" s="4">
+        <v>0</v>
+      </c>
+      <c r="I46" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J46" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="9">
+        <v>36</v>
+      </c>
+      <c r="B47" s="5">
+        <v>26</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="4">
+        <v>255</v>
+      </c>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H47" s="4">
+        <v>0</v>
+      </c>
+      <c r="I47" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J47" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="9">
+        <v>37</v>
+      </c>
+      <c r="B48" s="5">
+        <v>26</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="4">
+        <v>255</v>
+      </c>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H48" s="4">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J48" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="9">
+        <v>38</v>
+      </c>
+      <c r="B49" s="5">
+        <v>26</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="4">
+        <v>255</v>
+      </c>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H49" s="4">
+        <v>0</v>
+      </c>
+      <c r="I49" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J49" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="9">
+        <v>39</v>
+      </c>
+      <c r="B50" s="5">
+        <v>26</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="4">
+        <v>255</v>
+      </c>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H50" s="4">
+        <v>0</v>
+      </c>
+      <c r="I50" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J50" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="9">
+        <v>40</v>
+      </c>
+      <c r="B51" s="5">
+        <v>26</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="4">
+        <v>255</v>
+      </c>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H51" s="4">
+        <v>0</v>
+      </c>
+      <c r="I51" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J51" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="9">
+        <v>41</v>
+      </c>
+      <c r="B52" s="5">
+        <v>26</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="4">
+        <v>255</v>
+      </c>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H52" s="4">
+        <v>0</v>
+      </c>
+      <c r="I52" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J52" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="9">
+        <v>42</v>
+      </c>
+      <c r="B53" s="5">
+        <v>26</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="4">
+        <v>255</v>
+      </c>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H53" s="4">
+        <v>0</v>
+      </c>
+      <c r="I53" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J53" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="9">
+        <v>43</v>
+      </c>
+      <c r="B54" s="5">
+        <v>26</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="4">
+        <v>255</v>
+      </c>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H54" s="4">
+        <v>0</v>
+      </c>
+      <c r="I54" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J54" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="9">
+        <v>44</v>
+      </c>
+      <c r="B55" s="5">
+        <v>26</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="4">
+        <v>255</v>
+      </c>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H55" s="4">
+        <v>0</v>
+      </c>
+      <c r="I55" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J55" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="9">
+        <v>45</v>
+      </c>
+      <c r="B56" s="5">
+        <v>26</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="4">
+        <v>255</v>
+      </c>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H56" s="4">
+        <v>0</v>
+      </c>
+      <c r="I56" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J56" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="9">
+        <v>46</v>
+      </c>
+      <c r="B57" s="5">
+        <v>26</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="4">
+        <v>255</v>
+      </c>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H57" s="4">
+        <v>0</v>
+      </c>
+      <c r="I57" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J57" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="9">
+        <v>30</v>
+      </c>
+      <c r="B58" s="5">
+        <v>28</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="4">
+        <v>255</v>
+      </c>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H58" s="4">
+        <v>0</v>
+      </c>
+      <c r="I58" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="9">
+        <v>31</v>
+      </c>
+      <c r="B59" s="5">
+        <v>28</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="4">
+        <v>255</v>
+      </c>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H59" s="4">
+        <v>0</v>
+      </c>
+      <c r="I59" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J59" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="9">
+        <v>32</v>
+      </c>
+      <c r="B60" s="5">
+        <v>28</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="4">
+        <v>255</v>
+      </c>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H60" s="4">
+        <v>0</v>
+      </c>
+      <c r="I60" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J60" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="9">
+        <v>33</v>
+      </c>
+      <c r="B61" s="5">
+        <v>28</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" s="4">
+        <v>255</v>
+      </c>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H61" s="4">
+        <v>0</v>
+      </c>
+      <c r="I61" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J61" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="9">
+        <v>34</v>
+      </c>
+      <c r="B62" s="5">
+        <v>28</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" s="4">
+        <v>255</v>
+      </c>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H62" s="4">
+        <v>0</v>
+      </c>
+      <c r="I62" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J62" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="9">
+        <v>35</v>
+      </c>
+      <c r="B63" s="5">
+        <v>28</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" s="4">
+        <v>255</v>
+      </c>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H63" s="4">
+        <v>0</v>
+      </c>
+      <c r="I63" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J63" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="9">
+        <v>36</v>
+      </c>
+      <c r="B64" s="5">
+        <v>28</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="4">
+        <v>255</v>
+      </c>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H64" s="4">
+        <v>0</v>
+      </c>
+      <c r="I64" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J64" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="9">
+        <v>37</v>
+      </c>
+      <c r="B65" s="5">
+        <v>28</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D65" s="4">
+        <v>255</v>
+      </c>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H65" s="4">
+        <v>0</v>
+      </c>
+      <c r="I65" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J65" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="9">
+        <v>38</v>
+      </c>
+      <c r="B66" s="5">
+        <v>28</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" s="4">
+        <v>255</v>
+      </c>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="7">
+        <f t="shared" ref="G66:G74" ca="1" si="4">NOW()</f>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H66" s="4">
+        <v>0</v>
+      </c>
+      <c r="I66" s="7">
+        <f t="shared" ref="I66:I74" ca="1" si="5">NOW()</f>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J66" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A67" s="9">
+        <v>39</v>
+      </c>
+      <c r="B67" s="5">
+        <v>28</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" s="4">
+        <v>255</v>
+      </c>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="7">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H67" s="4">
+        <v>0</v>
+      </c>
+      <c r="I67" s="7">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J67" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="9">
+        <v>40</v>
+      </c>
+      <c r="B68" s="5">
+        <v>28</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" s="4">
+        <v>255</v>
+      </c>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="7">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H68" s="4">
+        <v>0</v>
+      </c>
+      <c r="I68" s="7">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J68" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A69" s="9">
+        <v>41</v>
+      </c>
+      <c r="B69" s="5">
+        <v>28</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" s="4">
+        <v>255</v>
+      </c>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="7">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H69" s="4">
+        <v>0</v>
+      </c>
+      <c r="I69" s="7">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J69" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A70" s="9">
+        <v>42</v>
+      </c>
+      <c r="B70" s="5">
+        <v>28</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="4">
+        <v>255</v>
+      </c>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="7">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H70" s="4">
+        <v>0</v>
+      </c>
+      <c r="I70" s="7">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J70" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="9">
+        <v>43</v>
+      </c>
+      <c r="B71" s="5">
+        <v>28</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" s="4">
+        <v>255</v>
+      </c>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="7">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H71" s="4">
+        <v>0</v>
+      </c>
+      <c r="I71" s="7">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J71" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A72" s="9">
+        <v>44</v>
+      </c>
+      <c r="B72" s="5">
+        <v>28</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" s="4">
+        <v>255</v>
+      </c>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="7">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H72" s="4">
+        <v>0</v>
+      </c>
+      <c r="I72" s="7">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J72" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A73" s="9">
+        <v>45</v>
+      </c>
+      <c r="B73" s="5">
+        <v>28</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="4">
+        <v>255</v>
+      </c>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="7">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H73" s="4">
+        <v>0</v>
+      </c>
+      <c r="I73" s="7">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J73" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A74" s="9">
+        <v>46</v>
+      </c>
+      <c r="B74" s="5">
+        <v>28</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" s="4">
+        <v>255</v>
+      </c>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="7">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="H74" s="4">
+        <v>0</v>
+      </c>
+      <c r="I74" s="7">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.442834374997</v>
+      </c>
+      <c r="J74" s="4">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
